--- a/py_dash_pcb_7_BOM.xlsx
+++ b/py_dash_pcb_7_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\racecar\programming_and_design\PyDash\PyDash_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD521E8-ADF1-4416-B4EE-602830C18397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794A2D80-EBA8-4A79-A4EF-E8FFCF02303E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="930" windowWidth="25515" windowHeight="12825" xr2:uid="{C634C7BF-3DA9-4665-B818-ADA65906E886}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C634C7BF-3DA9-4665-B818-ADA65906E886}"/>
   </bookViews>
   <sheets>
     <sheet name="py_dash_pcb_7" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="267">
   <si>
     <t>Reference</t>
   </si>
@@ -124,9 +124,6 @@
     <t>LED_SMD:LED_0805_2012Metric</t>
   </si>
   <si>
-    <t>D2,D3,D4,D5</t>
-  </si>
-  <si>
     <t>27V</t>
   </si>
   <si>
@@ -364,9 +361,6 @@
     <t>nBoot</t>
   </si>
   <si>
-    <t>774-219G-2ESF</t>
-  </si>
-  <si>
     <t>Button_Switch_SMD:SW_DIP_SPSTx01_Slide_6.7x4.1mm_W8.61mm_P2.54mm_LowProfile</t>
   </si>
   <si>
@@ -637,9 +631,6 @@
     <t>Diodes</t>
   </si>
   <si>
-    <t>219G-2ESF</t>
-  </si>
-  <si>
     <t>B3F-5050</t>
   </si>
   <si>
@@ -688,9 +679,6 @@
     <t>ok - 90k</t>
   </si>
   <si>
-    <t>CTS</t>
-  </si>
-  <si>
     <t>MCP2515T-E/ST</t>
   </si>
   <si>
@@ -806,6 +794,33 @@
   </si>
   <si>
     <t>Standoff_M2.5_6ET</t>
+  </si>
+  <si>
+    <t>490-DS04254201BK-SMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS04-254-2-01BK-SMT </t>
+  </si>
+  <si>
+    <t>Same Sky</t>
+  </si>
+  <si>
+    <t>2A 60V</t>
+  </si>
+  <si>
+    <t>D2,D3</t>
+  </si>
+  <si>
+    <t>D4,D5</t>
+  </si>
+  <si>
+    <t>750-CDBMT260-HF</t>
+  </si>
+  <si>
+    <t>CDBMT260-HF</t>
+  </si>
+  <si>
+    <t>Comchip</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B489D72-AD31-4579-A425-A1740584196B}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
@@ -1706,11 +1721,11 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J1" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K1" s="5">
-        <f>SUM(K3:K46)</f>
-        <v>158.13</v>
+        <f>SUM(K3:K47)</f>
+        <v>159.21000000000004</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,19 +1748,19 @@
         <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1768,19 +1783,19 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3">
         <v>0.17</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K46" si="0">J3*D3</f>
+        <f t="shared" ref="K3:K47" si="0">J3*D3</f>
         <v>1.7000000000000002</v>
       </c>
     </row>
@@ -1804,13 +1819,13 @@
         <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J4" s="3">
         <v>0.9</v>
@@ -1840,13 +1855,13 @@
         <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J5" s="3">
         <v>1.5</v>
@@ -1876,13 +1891,13 @@
         <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J6" s="3">
         <v>0.1</v>
@@ -1912,13 +1927,13 @@
         <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J7" s="3">
         <v>1.17</v>
@@ -1948,13 +1963,13 @@
         <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J8" s="3">
         <v>0.19</v>
@@ -1984,13 +1999,13 @@
         <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J9" s="3">
         <v>0.17</v>
@@ -2020,13 +2035,13 @@
         <v>32</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J10" s="3">
         <v>0.19</v>
@@ -2038,193 +2053,193 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="J11" s="3">
-        <v>0.12</v>
+        <v>0.71</v>
       </c>
       <c r="K11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.48</v>
+        <f t="shared" ref="K11" si="1">J11*D11</f>
+        <v>1.42</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J12" s="3">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="K12" s="5">
         <f t="shared" si="0"/>
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>178</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="J13" s="3">
+      <c r="H14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J14" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K14" s="5">
         <f t="shared" si="0"/>
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D14" s="2">
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D15" s="2">
         <v>16</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J14" s="6">
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J15" s="6">
         <v>1.24</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K15" s="5">
         <f t="shared" si="0"/>
         <v>19.84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3.38</v>
-      </c>
-      <c r="K15" s="5">
-        <f t="shared" si="0"/>
-        <v>3.38</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -2233,34 +2248,34 @@
         <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J16" s="3">
-        <v>1</v>
+        <v>3.38</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -2269,34 +2284,34 @@
         <v>8</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J17" s="3">
-        <v>1.1299999999999999</v>
+        <v>1</v>
       </c>
       <c r="K17" s="5">
         <f t="shared" si="0"/>
-        <v>1.1299999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -2305,34 +2320,34 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J18" s="3">
-        <v>18.350000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="0"/>
-        <v>18.350000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -2341,34 +2356,34 @@
         <v>8</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J19" s="3">
-        <v>1.76</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="0"/>
-        <v>1.76</v>
+        <v>18.350000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -2377,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J20" s="3">
         <v>1.76</v>
@@ -2398,13 +2413,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -2413,247 +2428,247 @@
         <v>8</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>202</v>
+        <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J21" s="3">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>73</v>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J22" s="3">
-        <v>30</v>
+        <v>2.1</v>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>256</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>257</v>
+        <v>71</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D23" s="2">
-        <v>6</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="6">
-        <v>0.2</v>
+        <v>198</v>
+      </c>
+      <c r="J23" s="3">
+        <v>30</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.42</v>
+        <v>153</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0.2</v>
       </c>
       <c r="K24" s="5">
         <f t="shared" si="0"/>
-        <v>0.42</v>
+        <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="J25" s="3">
         <v>0.42</v>
       </c>
       <c r="K25" s="5">
         <f t="shared" si="0"/>
-        <v>1.26</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="J26" s="3">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="K26" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="J27" s="3">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="K27" s="5">
         <f t="shared" si="0"/>
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -2662,106 +2677,106 @@
         <v>8</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H28" t="s">
-        <v>230</v>
+        <v>207</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="J28" s="3">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="K28" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D29" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>232</v>
+        <v>207</v>
+      </c>
+      <c r="H29" t="s">
+        <v>226</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="J29" s="3">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K29" s="5">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="J30" s="3">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -2770,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="J31" s="3">
         <v>0.1</v>
@@ -2791,13 +2806,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -2806,106 +2821,106 @@
         <v>8</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="K33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="K32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="2">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K33" s="5">
-        <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3">
         <v>0.1</v>
       </c>
       <c r="K34" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2914,34 +2929,34 @@
         <v>8</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J35" s="3">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K35" s="5">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -2950,142 +2965,142 @@
         <v>8</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="J36" s="3">
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
       <c r="K36" s="5">
         <f t="shared" si="0"/>
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>118</v>
+      <c r="F37" t="s">
+        <v>258</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>206</v>
+        <v>260</v>
+      </c>
+      <c r="H37" t="s">
+        <v>259</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="J37" s="6">
-        <v>0.34</v>
+        <v>221</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0.76</v>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" t="s">
-        <v>244</v>
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="J38" s="6">
-        <v>35</v>
+        <v>0.34</v>
       </c>
       <c r="K38" s="5">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>125</v>
+      <c r="E39" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" t="s">
+        <v>240</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>124</v>
+        <v>238</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="J39" s="6">
-        <v>2.09</v>
+        <v>35</v>
       </c>
       <c r="K39" s="5">
         <f t="shared" si="0"/>
-        <v>2.09</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -3094,34 +3109,34 @@
         <v>8</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>248</v>
+        <v>122</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="J40" s="6">
-        <v>0.6</v>
+        <v>2.09</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -3130,106 +3145,106 @@
         <v>8</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="J41" s="6">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="K41" s="5">
         <f t="shared" si="0"/>
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>236</v>
+        <v>164</v>
       </c>
       <c r="J42" s="6">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="K42" s="5">
         <f t="shared" si="0"/>
-        <v>3.64</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="J43" s="6">
-        <v>0.81</v>
+        <v>1.82</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" si="0"/>
-        <v>0.81</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -3238,34 +3253,34 @@
         <v>8</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="J44" s="6">
-        <v>3.05</v>
+        <v>0.81</v>
       </c>
       <c r="K44" s="5">
         <f t="shared" si="0"/>
-        <v>3.05</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -3274,34 +3289,34 @@
         <v>8</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="J45" s="6">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="K45" s="5">
         <f t="shared" si="0"/>
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -3310,28 +3325,64 @@
         <v>8</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J46" s="6">
+        <v>3.12</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="shared" si="0"/>
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J47" s="6">
         <v>1.0900000000000001</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K47" s="5">
         <f t="shared" si="0"/>
         <v>1.0900000000000001</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K46">
-    <sortCondition ref="A2:A46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K47">
+    <sortCondition ref="A2:A47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/py_dash_pcb_7_BOM.xlsx
+++ b/py_dash_pcb_7_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\racecar\programming_and_design\PyDash\PyDash_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794A2D80-EBA8-4A79-A4EF-E8FFCF02303E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6EB6EB-D4E5-420C-B54B-1368D11BBA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C634C7BF-3DA9-4665-B818-ADA65906E886}"/>
+    <workbookView xWindow="1485" yWindow="615" windowWidth="25515" windowHeight="14715" xr2:uid="{C634C7BF-3DA9-4665-B818-ADA65906E886}"/>
   </bookViews>
   <sheets>
     <sheet name="py_dash_pcb_7" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="266">
   <si>
     <t>Reference</t>
   </si>
@@ -454,12 +454,6 @@
     <t>U9</t>
   </si>
   <si>
-    <t>SN65HVD234</t>
-  </si>
-  <si>
-    <t>595-SN65HVD234DR</t>
-  </si>
-  <si>
     <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
   </si>
   <si>
@@ -682,9 +676,6 @@
     <t>MCP2515T-E/ST</t>
   </si>
   <si>
-    <t>SN65HVD234DR</t>
-  </si>
-  <si>
     <t>ok - 2k</t>
   </si>
   <si>
@@ -821,6 +812,12 @@
   </si>
   <si>
     <t>Comchip</t>
+  </si>
+  <si>
+    <t>SN65HVD231D</t>
+  </si>
+  <si>
+    <t>595-SN65HVD231DR</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1718,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J1" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K1" s="5">
         <f>SUM(K3:K47)</f>
@@ -1748,19 +1745,19 @@
         <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1783,13 +1780,13 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J3" s="3">
         <v>0.17</v>
@@ -1819,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J4" s="3">
         <v>0.9</v>
@@ -1855,13 +1852,13 @@
         <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J5" s="3">
         <v>1.5</v>
@@ -1891,13 +1888,13 @@
         <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J6" s="3">
         <v>0.1</v>
@@ -1927,13 +1924,13 @@
         <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J7" s="3">
         <v>1.17</v>
@@ -1963,13 +1960,13 @@
         <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="J8" s="3">
         <v>0.19</v>
@@ -1999,13 +1996,13 @@
         <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J9" s="3">
         <v>0.17</v>
@@ -2035,13 +2032,13 @@
         <v>32</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J10" s="3">
         <v>0.19</v>
@@ -2053,10 +2050,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>36</v>
@@ -2068,16 +2065,16 @@
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3">
         <v>0.71</v>
@@ -2089,7 +2086,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
@@ -2107,13 +2104,13 @@
         <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J12" s="3">
         <v>0.12</v>
@@ -2143,13 +2140,13 @@
         <v>39</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="J13" s="3">
         <v>0.34</v>
@@ -2179,13 +2176,13 @@
         <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J14" s="3">
         <v>1.1599999999999999</v>
@@ -2200,10 +2197,10 @@
         <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2">
         <v>16</v>
@@ -2212,16 +2209,16 @@
         <v>8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J15" s="6">
         <v>1.24</v>
@@ -2251,13 +2248,13 @@
         <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J16" s="3">
         <v>3.38</v>
@@ -2287,13 +2284,13 @@
         <v>53</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>52</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J17" s="3">
         <v>1</v>
@@ -2323,13 +2320,13 @@
         <v>57</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J18" s="3">
         <v>1.1299999999999999</v>
@@ -2359,13 +2356,13 @@
         <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J19" s="3">
         <v>18.350000000000001</v>
@@ -2395,13 +2392,13 @@
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J20" s="3">
         <v>1.76</v>
@@ -2431,13 +2428,13 @@
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J21" s="3">
         <v>1.76</v>
@@ -2464,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="J22" s="3">
         <v>2.1</v>
@@ -2509,7 +2506,7 @@
         <v>73</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J23" s="3">
         <v>30</v>
@@ -2521,10 +2518,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -2533,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J24" s="6">
         <v>0.2</v>
@@ -2572,13 +2569,13 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J25" s="3">
         <v>0.42</v>
@@ -2608,13 +2605,13 @@
         <v>80</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J26" s="3">
         <v>0.42</v>
@@ -2641,16 +2638,16 @@
         <v>8</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="J27" s="3">
         <v>0.1</v>
@@ -2680,13 +2677,13 @@
         <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J28" s="3">
         <v>0.19</v>
@@ -2716,13 +2713,13 @@
         <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J29" s="3">
         <v>0.1</v>
@@ -2752,13 +2749,13 @@
         <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J30" s="3">
         <v>0.12</v>
@@ -2788,13 +2785,13 @@
         <v>86</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J31" s="3">
         <v>0.1</v>
@@ -2824,13 +2821,13 @@
         <v>110</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J32" s="3">
         <v>0.1</v>
@@ -2860,13 +2857,13 @@
         <v>89</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J33" s="3">
         <v>0.15</v>
@@ -2896,13 +2893,13 @@
         <v>92</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3">
         <v>0.1</v>
@@ -2932,13 +2929,13 @@
         <v>95</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3">
         <v>0.1</v>
@@ -2968,13 +2965,13 @@
         <v>98</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J36" s="3">
         <v>0.12</v>
@@ -3001,16 +2998,16 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H37" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J37" s="3">
         <v>0.76</v>
@@ -3040,13 +3037,13 @@
         <v>116</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J38" s="6">
         <v>0.34</v>
@@ -3070,19 +3067,19 @@
         <v>1</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F39" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="J39" s="6">
         <v>35</v>
@@ -3112,13 +3109,13 @@
         <v>123</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J40" s="6">
         <v>2.09</v>
@@ -3145,16 +3142,16 @@
         <v>8</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J41" s="6">
         <v>0.6</v>
@@ -3184,13 +3181,13 @@
         <v>130</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>129</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J42" s="6">
         <v>1.03</v>
@@ -3220,13 +3217,13 @@
         <v>134</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>133</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J43" s="6">
         <v>1.82</v>
@@ -3253,16 +3250,16 @@
         <v>8</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J44" s="6">
         <v>0.81</v>
@@ -3292,13 +3289,13 @@
         <v>141</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J45" s="6">
         <v>3.05</v>
@@ -3313,10 +3310,10 @@
         <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -3324,17 +3321,17 @@
       <c r="E46" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>145</v>
+      <c r="F46" t="s">
+        <v>265</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H46" t="s">
+        <v>264</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="J46" s="6">
         <v>3.12</v>
@@ -3346,13 +3343,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -3361,16 +3358,16 @@
         <v>8</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J47" s="6">
         <v>1.0900000000000001</v>
